--- a/testCases/Lereve Manual Testing.xlsx
+++ b/testCases/Lereve Manual Testing.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="78">
   <si>
     <t>Please click here to see the full  pdf</t>
   </si>
@@ -170,7 +170,13 @@
     <t>Final Status</t>
   </si>
   <si>
+    <t>Header Module</t>
+  </si>
+  <si>
     <t>UI Testing</t>
+  </si>
+  <si>
+    <t>Header Section</t>
   </si>
   <si>
     <t>Verify header section is displayed on the website</t>
@@ -187,6 +193,66 @@
   </si>
   <si>
     <t>Passed</t>
+  </si>
+  <si>
+    <t>Header
+ Alignment</t>
+  </si>
+  <si>
+    <t>Logo Alignment</t>
+  </si>
+  <si>
+    <t>Header 
+Consistency</t>
+  </si>
+  <si>
+    <t>Icons &amp; Text</t>
+  </si>
+  <si>
+    <t>Dropdown Menu</t>
+  </si>
+  <si>
+    <t>Not found as per as 
+expectation</t>
+  </si>
+  <si>
+    <t>Functional 
+Testing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header Links
+</t>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>Logo Navigation</t>
+  </si>
+  <si>
+    <t>Search Bar</t>
+  </si>
+  <si>
+    <t>Search Module</t>
+  </si>
+  <si>
+    <t>Search Field</t>
+  </si>
+  <si>
+    <t>Verify spelling and grammar 
+of placeholder</t>
+  </si>
+  <si>
+    <t>Text should be correct</t>
+  </si>
+  <si>
+    <t>Found as per as expectations</t>
+  </si>
+  <si>
+    <t>Oprn Page</t>
+  </si>
+  <si>
+    <t>Search Icon</t>
   </si>
   <si>
     <t>t</t>
@@ -199,7 +265,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -252,6 +318,20 @@
     </font>
     <font>
       <b/>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12.0"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -350,7 +430,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="32">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -410,10 +490,16 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -424,6 +510,18 @@
     </xf>
     <xf borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -887,8 +985,10 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="5" max="5" width="13.25"/>
-    <col customWidth="1" min="7" max="7" width="15.38"/>
+    <col customWidth="1" min="4" max="4" width="22.13"/>
+    <col customWidth="1" min="5" max="5" width="19.5"/>
+    <col customWidth="1" min="6" max="6" width="22.88"/>
+    <col customWidth="1" min="7" max="7" width="17.63"/>
     <col customWidth="1" min="8" max="8" width="13.88"/>
   </cols>
   <sheetData>
@@ -962,51 +1062,193 @@
       <c r="Y5" s="20"/>
       <c r="Z5" s="20"/>
     </row>
-    <row r="6">
-      <c r="A6" s="21">
+    <row r="6" ht="31.5" customHeight="1">
+      <c r="A6" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22"/>
+      <c r="R6" s="22"/>
+      <c r="S6" s="22"/>
+      <c r="T6" s="22"/>
+      <c r="U6" s="22"/>
+      <c r="V6" s="22"/>
+      <c r="W6" s="22"/>
+      <c r="X6" s="22"/>
+      <c r="Y6" s="22"/>
+      <c r="Z6" s="22"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="23">
         <v>1.0</v>
       </c>
-      <c r="B6" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="23" t="s">
+      <c r="B7" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="C7" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="D7" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="E7" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="H6" s="20"/>
-      <c r="I6" s="25" t="s">
+      <c r="F7" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
-      <c r="N6" s="20"/>
-      <c r="O6" s="20"/>
-      <c r="P6" s="20"/>
-      <c r="Q6" s="20"/>
-      <c r="R6" s="20"/>
-      <c r="S6" s="20"/>
-      <c r="T6" s="20"/>
-      <c r="U6" s="20"/>
-      <c r="V6" s="20"/>
-      <c r="W6" s="20"/>
-      <c r="X6" s="20"/>
-      <c r="Y6" s="20"/>
-      <c r="Z6" s="20"/>
-    </row>
+      <c r="G7" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" s="20"/>
+      <c r="I7" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20"/>
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
+      <c r="U7" s="20"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="20"/>
+      <c r="X7" s="20"/>
+      <c r="Y7" s="20"/>
+      <c r="Z7" s="20"/>
+    </row>
+    <row r="8" ht="48.75" customHeight="1">
+      <c r="A8" s="28">
+        <v>2.0</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" ht="47.25" customHeight="1">
+      <c r="A9" s="9">
+        <v>3.0</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" ht="49.5" customHeight="1">
+      <c r="A10" s="9">
+        <v>4.0</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" ht="54.0" customHeight="1">
+      <c r="A11" s="9">
+        <v>5.0</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" ht="52.5" customHeight="1">
+      <c r="A12" s="9">
+        <v>6.0</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" ht="46.5" customHeight="1">
+      <c r="B13" s="29" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" ht="51.75" customHeight="1">
+      <c r="A14" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" ht="60.0" customHeight="1">
+      <c r="A15" s="9">
+        <v>8.0</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" ht="52.5" customHeight="1">
+      <c r="A16" s="9">
+        <v>9.0</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" ht="52.5" customHeight="1">
+      <c r="A17" s="9">
+        <v>10.0</v>
+      </c>
+      <c r="C17" s="29" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" ht="52.5" customHeight="1">
+      <c r="A18" s="30" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" ht="52.5" customHeight="1">
+      <c r="B19" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" ht="52.5" customHeight="1">
+      <c r="C20" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" ht="52.5" customHeight="1">
+      <c r="C21" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" ht="52.5" customHeight="1"/>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A18:I18"/>
+  </mergeCells>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="B1"/>
   </hyperlinks>
@@ -1023,7 +1265,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/testCases/Lereve Manual Testing.xlsx
+++ b/testCases/Lereve Manual Testing.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="86">
   <si>
     <t>Please click here to see the full  pdf</t>
   </si>
@@ -249,10 +249,36 @@
     <t>Found as per as expectations</t>
   </si>
   <si>
-    <t>Oprn Page</t>
+    <t>Open Page</t>
   </si>
   <si>
     <t>Search Icon</t>
+  </si>
+  <si>
+    <t>Verify search with valid 
+keyword</t>
+  </si>
+  <si>
+    <t>Verify search using Enter key</t>
+  </si>
+  <si>
+    <t>Pagination</t>
+  </si>
+  <si>
+    <t>Verify pagination appears</t>
+  </si>
+  <si>
+    <t>Search Results</t>
+  </si>
+  <si>
+    <t>Verify related keywords 
+shown</t>
+  </si>
+  <si>
+    <t>Footer</t>
+  </si>
+  <si>
+    <t>Footer Section</t>
   </si>
   <si>
     <t>t</t>
@@ -1243,11 +1269,84 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" ht="52.5" customHeight="1"/>
+    <row r="22" ht="52.5" customHeight="1">
+      <c r="B22" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" ht="62.25" customHeight="1">
+      <c r="C23" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" ht="62.25" customHeight="1">
+      <c r="C24" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" ht="62.25" customHeight="1">
+      <c r="C25" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" ht="62.25" customHeight="1">
+      <c r="C26" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" ht="62.25" customHeight="1">
+      <c r="A27" s="30" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" ht="62.25" customHeight="1">
+      <c r="B28" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" ht="62.25" customHeight="1">
+      <c r="C29" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" ht="62.25" customHeight="1"/>
+    <row r="31" ht="62.25" customHeight="1"/>
+    <row r="32" ht="62.25" customHeight="1"/>
+    <row r="33" ht="62.25" customHeight="1"/>
+    <row r="34" ht="62.25" customHeight="1"/>
+    <row r="35" ht="62.25" customHeight="1"/>
+    <row r="36" ht="62.25" customHeight="1"/>
+    <row r="37" ht="62.25" customHeight="1"/>
+    <row r="38" ht="62.25" customHeight="1"/>
+    <row r="39" ht="62.25" customHeight="1"/>
+    <row r="40" ht="62.25" customHeight="1"/>
+    <row r="41" ht="62.25" customHeight="1"/>
+    <row r="42" ht="62.25" customHeight="1"/>
+    <row r="43" ht="62.25" customHeight="1"/>
+    <row r="44" ht="62.25" customHeight="1"/>
+    <row r="45" ht="62.25" customHeight="1"/>
+    <row r="46" ht="62.25" customHeight="1"/>
+    <row r="47" ht="62.25" customHeight="1"/>
+    <row r="48" ht="62.25" customHeight="1"/>
+    <row r="49" ht="62.25" customHeight="1"/>
+    <row r="50" ht="62.25" customHeight="1"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A6:I6"/>
     <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A27:I27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="B1"/>
@@ -1265,7 +1364,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/testCases/Lereve Manual Testing.xlsx
+++ b/testCases/Lereve Manual Testing.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="113">
   <si>
     <t>Please click here to see the full  pdf</t>
   </si>
@@ -278,7 +278,99 @@
     <t>Footer</t>
   </si>
   <si>
-    <t>Footer Section</t>
+    <t>Footer Alignment</t>
+  </si>
+  <si>
+    <t>Verify footer section 
+alignment</t>
+  </si>
+  <si>
+    <t>Footer 
+Consistency</t>
+  </si>
+  <si>
+    <t>Verify same footer appears 
+on all pages</t>
+  </si>
+  <si>
+    <t>Follow Us Section</t>
+  </si>
+  <si>
+    <t>Verify correctness of social 
+media icons in Follow Us 
+section</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>Verify year &amp; icon displayed</t>
+  </si>
+  <si>
+    <t>Footer Links</t>
+  </si>
+  <si>
+    <t>Verify all footer links are click-
+-able</t>
+  </si>
+  <si>
+    <t>Verify correct page opens on 
+clicking header links</t>
+  </si>
+  <si>
+    <t>Social Links</t>
+  </si>
+  <si>
+    <t>Verify social icons redirect 
+correctly</t>
+  </si>
+  <si>
+    <t>Login Module</t>
+  </si>
+  <si>
+    <t>Placeholder</t>
+  </si>
+  <si>
+    <t>Verify placeholder text in fields</t>
+  </si>
+  <si>
+    <t>Post Login UI</t>
+  </si>
+  <si>
+    <t>Verify Sign Up not shown after 
+login</t>
+  </si>
+  <si>
+    <t>Spelling</t>
+  </si>
+  <si>
+    <t>Verify spelling mistakes</t>
+  </si>
+  <si>
+    <t>Login Page</t>
+  </si>
+  <si>
+    <t>Verify login page loads properly</t>
+  </si>
+  <si>
+    <t>Valid Login</t>
+  </si>
+  <si>
+    <t>Verify login with valid phone
+number and OTP</t>
+  </si>
+  <si>
+    <t>Invalid Login</t>
+  </si>
+  <si>
+    <t>Verify error message for invalid
+OTP</t>
+  </si>
+  <si>
+    <t>Keyboard</t>
+  </si>
+  <si>
+    <t>Verify login using Enter key</t>
   </si>
   <si>
     <t>t</t>
@@ -1011,8 +1103,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="4" max="4" width="22.13"/>
-    <col customWidth="1" min="5" max="5" width="19.5"/>
+    <col customWidth="1" min="3" max="3" width="14.13"/>
+    <col customWidth="1" min="4" max="4" width="23.63"/>
+    <col customWidth="1" min="5" max="5" width="22.75"/>
     <col customWidth="1" min="6" max="6" width="22.88"/>
     <col customWidth="1" min="7" max="7" width="17.63"/>
     <col customWidth="1" min="8" max="8" width="13.88"/>
@@ -1320,33 +1413,144 @@
       <c r="C29" s="9" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="30" ht="62.25" customHeight="1"/>
-    <row r="31" ht="62.25" customHeight="1"/>
-    <row r="32" ht="62.25" customHeight="1"/>
-    <row r="33" ht="62.25" customHeight="1"/>
-    <row r="34" ht="62.25" customHeight="1"/>
-    <row r="35" ht="62.25" customHeight="1"/>
-    <row r="36" ht="62.25" customHeight="1"/>
-    <row r="37" ht="62.25" customHeight="1"/>
-    <row r="38" ht="62.25" customHeight="1"/>
-    <row r="39" ht="62.25" customHeight="1"/>
-    <row r="40" ht="62.25" customHeight="1"/>
-    <row r="41" ht="62.25" customHeight="1"/>
-    <row r="42" ht="62.25" customHeight="1"/>
-    <row r="43" ht="62.25" customHeight="1"/>
-    <row r="44" ht="62.25" customHeight="1"/>
-    <row r="45" ht="62.25" customHeight="1"/>
-    <row r="46" ht="62.25" customHeight="1"/>
+      <c r="D29" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" ht="62.25" customHeight="1">
+      <c r="C30" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" ht="62.25" customHeight="1">
+      <c r="C31" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="32" ht="62.25" customHeight="1">
+      <c r="C32" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" ht="62.25" customHeight="1">
+      <c r="B33" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" ht="62.25" customHeight="1">
+      <c r="C34" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" ht="62.25" customHeight="1">
+      <c r="C35" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="36" ht="62.25" customHeight="1">
+      <c r="C36" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="37" ht="62.25" customHeight="1">
+      <c r="A37" s="30" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38" ht="62.25" customHeight="1">
+      <c r="B38" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="39" ht="62.25" customHeight="1">
+      <c r="C39" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" ht="62.25" customHeight="1">
+      <c r="C40" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="41" ht="62.25" customHeight="1">
+      <c r="C41" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="42" ht="62.25" customHeight="1">
+      <c r="B42" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="43" ht="62.25" customHeight="1">
+      <c r="C43" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="44" ht="62.25" customHeight="1">
+      <c r="C44" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="45" ht="62.25" customHeight="1">
+      <c r="C45" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="46" ht="62.25" customHeight="1">
+      <c r="C46" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>111</v>
+      </c>
+    </row>
     <row r="47" ht="62.25" customHeight="1"/>
     <row r="48" ht="62.25" customHeight="1"/>
     <row r="49" ht="62.25" customHeight="1"/>
     <row r="50" ht="62.25" customHeight="1"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A6:I6"/>
     <mergeCell ref="A18:I18"/>
     <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A37:I37"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="B1"/>
@@ -1364,7 +1568,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/testCases/Lereve Manual Testing.xlsx
+++ b/testCases/Lereve Manual Testing.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="143">
   <si>
     <t>Please click here to see the full  pdf</t>
   </si>
@@ -132,6 +132,15 @@
   </si>
   <si>
     <t>Verify contact us page UI, form validation, submission, and link redirections</t>
+  </si>
+  <si>
+    <t>TS-10</t>
+  </si>
+  <si>
+    <t>Categories</t>
+  </si>
+  <si>
+    <t>Verify Category Navigation, Dropdown Menu, and Product Filtering Functionality</t>
   </si>
   <si>
     <t>Product Name</t>
@@ -199,17 +208,44 @@
  Alignment</t>
   </si>
   <si>
+    <t>Verify header section alignment</t>
+  </si>
+  <si>
+    <t>Header elements should be 
+properly aligned</t>
+  </si>
+  <si>
     <t>Logo Alignment</t>
+  </si>
+  <si>
+    <t>Verify website logo alignment 
+in header</t>
+  </si>
+  <si>
+    <t>Logo should be properly 
+aligned</t>
   </si>
   <si>
     <t>Header 
 Consistency</t>
   </si>
   <si>
+    <t>Verify same header appears on 
+all pages</t>
+  </si>
+  <si>
     <t>Icons &amp; Text</t>
   </si>
   <si>
+    <t>Verify icons are aligned with the
+text</t>
+  </si>
+  <si>
     <t>Dropdown Menu</t>
+  </si>
+  <si>
+    <t>Verify dropdown opens on 
+hover/click</t>
   </si>
   <si>
     <t>Not found as per as 
@@ -224,13 +260,29 @@
 </t>
   </si>
   <si>
+    <t>Verify all header links are 
+clickable</t>
+  </si>
+  <si>
     <t>Navigation</t>
   </si>
   <si>
+    <t>Verify correct page opens on 
+clicking header links</t>
+  </si>
+  <si>
     <t>Logo Navigation</t>
   </si>
   <si>
+    <t>Verify clicking logo opens 
+homepage</t>
+  </si>
+  <si>
     <t>Search Bar</t>
+  </si>
+  <si>
+    <t>Verify search bar is present in 
+header</t>
   </si>
   <si>
     <t>Search Module</t>
@@ -253,6 +305,12 @@
   </si>
   <si>
     <t>Search Icon</t>
+  </si>
+  <si>
+    <t>Verify search icon presence</t>
+  </si>
+  <si>
+    <t>Verify hover effect on icon</t>
   </si>
   <si>
     <t>Verify search with valid 
@@ -314,10 +372,6 @@
 -able</t>
   </si>
   <si>
-    <t>Verify correct page opens on 
-clicking header links</t>
-  </si>
-  <si>
     <t>Social Links</t>
   </si>
   <si>
@@ -364,6 +418,10 @@
   </si>
   <si>
     <t>Verify error message for invalid
+phone number</t>
+  </si>
+  <si>
+    <t>Verify error message for invalid
 OTP</t>
   </si>
   <si>
@@ -371,6 +429,56 @@
   </si>
   <si>
     <t>Verify login using Enter key</t>
+  </si>
+  <si>
+    <t>Categories Module (https://www.lerevecraze.com/product-category)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI Testing </t>
+  </si>
+  <si>
+    <t>Category Text</t>
+  </si>
+  <si>
+    <t>Verify category names are 
+spelled correctly</t>
+  </si>
+  <si>
+    <t>Category Hover</t>
+  </si>
+  <si>
+    <t>Verify dropdown appears on 
+hover for each category</t>
+  </si>
+  <si>
+    <t>Category Click</t>
+  </si>
+  <si>
+    <t>Verify clicking on category 
+navigates to category page</t>
+  </si>
+  <si>
+    <t>Dropdown Display</t>
+  </si>
+  <si>
+    <t>Verify subcategories are 
+displayed in dropdown</t>
+  </si>
+  <si>
+    <t>Product Sorting</t>
+  </si>
+  <si>
+    <t>Verify products can be sorted 
+correctly using all available 
+sorting options</t>
+  </si>
+  <si>
+    <t>Product Filtering</t>
+  </si>
+  <si>
+    <t>Verify products can be filtered 
+correctly using all available 
+filter options</t>
   </si>
   <si>
     <t>t</t>
@@ -548,7 +656,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -569,69 +677,72 @@
     <xf borderId="2" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
@@ -640,12 +751,77 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="1">
+    <tableStyle count="4" pivot="0" name="test_scenario-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    </tableStyle>
+  </tableStyles>
 </styleSheet>
 </file>
 
@@ -700,6 +876,18 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A8:D18" displayName="Table1" name="Table1" id="1">
+  <tableColumns count="4">
+    <tableColumn name="Test Scenario ID" id="1"/>
+    <tableColumn name="Reference" id="2"/>
+    <tableColumn name="Test Scenario Description" id="3"/>
+    <tableColumn name="Number of Test Cases" id="4"/>
+  </tableColumns>
+  <tableStyleInfo name="test_scenario-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -923,9 +1111,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.0"/>
+    <col customWidth="1" min="1" max="1" width="17.63"/>
     <col customWidth="1" min="2" max="2" width="16.38"/>
-    <col customWidth="1" min="3" max="3" width="78.38"/>
+    <col customWidth="1" min="3" max="3" width="37.63"/>
     <col customWidth="1" min="4" max="4" width="25.13"/>
   </cols>
   <sheetData>
@@ -969,7 +1157,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="5"/>
     </row>
-    <row r="8">
+    <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="8" t="s">
         <v>8</v>
       </c>
@@ -983,7 +1171,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="9" t="s">
         <v>12</v>
       </c>
@@ -993,8 +1181,11 @@
       <c r="C9" s="10" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10">
+      <c r="D9" s="9">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="9" t="s">
         <v>15</v>
       </c>
@@ -1004,8 +1195,11 @@
       <c r="C10" s="11" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11">
+      <c r="D10" s="9">
+        <v>26.0</v>
+      </c>
+    </row>
+    <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="9" t="s">
         <v>18</v>
       </c>
@@ -1015,8 +1209,11 @@
       <c r="C11" s="10" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="12">
+      <c r="D11" s="9">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="9" t="s">
         <v>21</v>
       </c>
@@ -1026,8 +1223,11 @@
       <c r="C12" s="12" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="13">
+      <c r="D12" s="9">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="9" t="s">
         <v>24</v>
       </c>
@@ -1037,8 +1237,11 @@
       <c r="C13" s="9" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="14">
+      <c r="D13" s="9">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="9" t="s">
         <v>27</v>
       </c>
@@ -1048,8 +1251,11 @@
       <c r="C14" s="10" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="15">
+      <c r="D14" s="9">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="9" t="s">
         <v>30</v>
       </c>
@@ -1059,8 +1265,11 @@
       <c r="C15" s="13" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="16">
+      <c r="D15" s="9">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="9" t="s">
         <v>33</v>
       </c>
@@ -1070,8 +1279,11 @@
       <c r="C16" s="10" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="17">
+      <c r="D16" s="9">
+        <v>30.0</v>
+      </c>
+    </row>
+    <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="9" t="s">
         <v>36</v>
       </c>
@@ -1080,6 +1292,23 @@
       </c>
       <c r="C17" s="10" t="s">
         <v>38</v>
+      </c>
+      <c r="D17" s="9">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="18" ht="22.5" customHeight="1">
+      <c r="A18" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="9">
+        <v>20.0</v>
       </c>
     </row>
   </sheetData>
@@ -1093,6 +1322,9 @@
     <hyperlink r:id="rId1" ref="B2"/>
   </hyperlinks>
   <drawing r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId4"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -1104,7 +1336,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="3" max="3" width="14.13"/>
-    <col customWidth="1" min="4" max="4" width="23.63"/>
+    <col customWidth="1" min="4" max="4" width="24.0"/>
     <col customWidth="1" min="5" max="5" width="22.75"/>
     <col customWidth="1" min="6" max="6" width="22.88"/>
     <col customWidth="1" min="7" max="7" width="17.63"/>
@@ -1113,7 +1345,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>2</v>
@@ -1121,7 +1353,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B2" s="15">
         <v>46109.0</v>
@@ -1129,7 +1361,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B3" s="16">
         <v>46117.0</v>
@@ -1137,31 +1369,31 @@
     </row>
     <row r="5" ht="31.5" customHeight="1">
       <c r="A5" s="17" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="I5" s="18" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J5" s="20"/>
       <c r="K5" s="20"/>
@@ -1183,7 +1415,7 @@
     </row>
     <row r="6" ht="31.5" customHeight="1">
       <c r="A6" s="21" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J6" s="22"/>
       <c r="K6" s="22"/>
@@ -1208,26 +1440,26 @@
         <v>1.0</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G7" s="26" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H7" s="20"/>
       <c r="I7" s="27" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J7" s="20"/>
       <c r="K7" s="20"/>
@@ -1251,306 +1483,436 @@
       <c r="A8" s="28">
         <v>2.0</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" s="29" t="s">
         <v>59</v>
       </c>
+      <c r="G8" s="29" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="9" ht="47.25" customHeight="1">
-      <c r="A9" s="9">
+      <c r="A9" s="29">
         <v>3.0</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="29" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="10" ht="49.5" customHeight="1">
-      <c r="A10" s="9">
+      <c r="A10" s="29">
         <v>4.0</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>61</v>
+      <c r="C10" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="11" ht="54.0" customHeight="1">
-      <c r="A11" s="9">
+      <c r="A11" s="29">
         <v>5.0</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>62</v>
+      <c r="C11" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="12" ht="52.5" customHeight="1">
-      <c r="A12" s="9">
+      <c r="A12" s="29">
         <v>6.0</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>64</v>
+      <c r="C12" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" s="29" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="13" ht="46.5" customHeight="1">
-      <c r="B13" s="29" t="s">
-        <v>65</v>
+      <c r="B13" s="30" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="14" ht="51.75" customHeight="1">
-      <c r="A14" s="9">
+      <c r="A14" s="29">
         <v>7.0</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>66</v>
+        <v>76</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="15" ht="60.0" customHeight="1">
-      <c r="A15" s="9">
+      <c r="A15" s="29">
         <v>8.0</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>67</v>
+        <v>78</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="16" ht="52.5" customHeight="1">
-      <c r="A16" s="9">
+      <c r="A16" s="29">
         <v>9.0</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>68</v>
+        <v>80</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="17" ht="52.5" customHeight="1">
-      <c r="A17" s="9">
+      <c r="A17" s="29">
         <v>10.0</v>
       </c>
-      <c r="C17" s="29" t="s">
-        <v>69</v>
+      <c r="C17" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="29" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="18" ht="52.5" customHeight="1">
-      <c r="A18" s="30" t="s">
-        <v>70</v>
+      <c r="A18" s="31" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="19" ht="52.5" customHeight="1">
-      <c r="B19" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D19" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G19" s="9" t="s">
+      <c r="B19" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="D19" s="32" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="F19" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="G19" s="29" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="20" ht="52.5" customHeight="1">
+      <c r="C20" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" s="29" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" ht="52.5" customHeight="1">
+      <c r="C21" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="29" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" ht="52.5" customHeight="1">
+      <c r="B22" s="29" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="20" ht="52.5" customHeight="1">
-      <c r="C20" s="9" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21" ht="52.5" customHeight="1">
-      <c r="C21" s="9" t="s">
+    <row r="23" ht="62.25" customHeight="1">
+      <c r="C23" s="29" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="22" ht="52.5" customHeight="1">
-      <c r="B22" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" ht="62.25" customHeight="1">
-      <c r="C23" s="9" t="s">
+      <c r="D23" s="29" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" ht="62.25" customHeight="1">
+      <c r="C24" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="24" ht="62.25" customHeight="1">
-      <c r="C24" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="29" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="25" ht="62.25" customHeight="1">
+      <c r="C25" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="D25" s="29" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" ht="62.25" customHeight="1">
+      <c r="C26" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" s="29" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="27" ht="62.25" customHeight="1">
+      <c r="A27" s="31" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="28" ht="62.25" customHeight="1">
+      <c r="B28" s="29" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" ht="62.25" customHeight="1">
+      <c r="C29" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" s="29" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" ht="62.25" customHeight="1">
+      <c r="C30" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="D30" s="29" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" ht="62.25" customHeight="1">
+      <c r="C31" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="D31" s="29" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" ht="62.25" customHeight="1">
+      <c r="C32" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="D32" s="29" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="33" ht="62.25" customHeight="1">
+      <c r="B33" s="29" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="34" ht="62.25" customHeight="1">
+      <c r="C34" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="D34" s="29" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="35" ht="62.25" customHeight="1">
+      <c r="C35" s="29" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="25" ht="62.25" customHeight="1">
-      <c r="C25" s="9" t="s">
+      <c r="D35" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="D25" s="9" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="26" ht="62.25" customHeight="1">
-      <c r="C26" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27" ht="62.25" customHeight="1">
-      <c r="A27" s="30" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="28" ht="62.25" customHeight="1">
-      <c r="B28" s="9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="29" ht="62.25" customHeight="1">
-      <c r="C29" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="30" ht="62.25" customHeight="1">
-      <c r="C30" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="31" ht="62.25" customHeight="1">
-      <c r="C31" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="32" ht="62.25" customHeight="1">
-      <c r="C32" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="33" ht="62.25" customHeight="1">
-      <c r="B33" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="34" ht="62.25" customHeight="1">
-      <c r="C34" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="35" ht="62.25" customHeight="1">
-      <c r="C35" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>94</v>
-      </c>
     </row>
     <row r="36" ht="62.25" customHeight="1">
-      <c r="C36" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>96</v>
+      <c r="C36" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="D36" s="29" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="37" ht="62.25" customHeight="1">
-      <c r="A37" s="30" t="s">
-        <v>97</v>
+      <c r="A37" s="31" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="38" ht="62.25" customHeight="1">
-      <c r="B38" s="9" t="s">
-        <v>52</v>
+      <c r="B38" s="29" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="39" ht="62.25" customHeight="1">
-      <c r="C39" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>99</v>
+      <c r="C39" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="D39" s="29" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="40" ht="62.25" customHeight="1">
-      <c r="C40" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>101</v>
+      <c r="C40" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="D40" s="29" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="41" ht="62.25" customHeight="1">
-      <c r="C41" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>103</v>
+      <c r="C41" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="D41" s="29" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="42" ht="62.25" customHeight="1">
-      <c r="B42" s="9" t="s">
-        <v>65</v>
+      <c r="B42" s="29" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="43" ht="62.25" customHeight="1">
-      <c r="C43" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>105</v>
+      <c r="C43" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="D43" s="29" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="44" ht="62.25" customHeight="1">
-      <c r="C44" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>107</v>
+      <c r="C44" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="D44" s="29" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="45" ht="62.25" customHeight="1">
-      <c r="C45" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>109</v>
+      <c r="C45" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="D45" s="29" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="46" ht="62.25" customHeight="1">
-      <c r="C46" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="47" ht="62.25" customHeight="1"/>
-    <row r="48" ht="62.25" customHeight="1"/>
-    <row r="49" ht="62.25" customHeight="1"/>
-    <row r="50" ht="62.25" customHeight="1"/>
+      <c r="C46" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="D46" s="29" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="47" ht="62.25" customHeight="1">
+      <c r="C47" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="D47" s="29" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="48" ht="62.25" customHeight="1">
+      <c r="A48" s="28" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="49" ht="62.25" customHeight="1">
+      <c r="B49" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="C49" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="D49" s="29" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="50" ht="62.25" customHeight="1">
+      <c r="B50" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="C50" s="29"/>
+      <c r="D50" s="29"/>
+    </row>
+    <row r="51" ht="62.25" customHeight="1">
+      <c r="B51" s="29"/>
+      <c r="C51" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="D51" s="29" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="52" ht="62.25" customHeight="1">
+      <c r="C52" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="D52" s="29" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="53" ht="61.5" customHeight="1">
+      <c r="C53" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="D53" s="29" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="54" ht="61.5" customHeight="1">
+      <c r="C54" s="29" t="s">
+        <v>138</v>
+      </c>
+      <c r="D54" s="29" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="55" ht="61.5" customHeight="1">
+      <c r="C55" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="D55" s="29" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="56" ht="61.5" customHeight="1"/>
+    <row r="57" ht="61.5" customHeight="1"/>
+    <row r="58" ht="61.5" customHeight="1"/>
+    <row r="59" ht="61.5" customHeight="1"/>
+    <row r="60" ht="61.5" customHeight="1"/>
+    <row r="61" ht="61.5" customHeight="1"/>
+    <row r="62" ht="61.5" customHeight="1"/>
+    <row r="63" ht="61.5" customHeight="1"/>
+    <row r="64" ht="61.5" customHeight="1"/>
+    <row r="65" ht="61.5" customHeight="1"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A6:I6"/>
     <mergeCell ref="A18:I18"/>
     <mergeCell ref="A27:I27"/>
     <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A48:I48"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="B1"/>
@@ -1567,8 +1929,8 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="s">
-        <v>112</v>
+      <c r="A1" s="29" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/testCases/Lereve Manual Testing.xlsx
+++ b/testCases/Lereve Manual Testing.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="178">
   <si>
     <t>Please click here to see the full  pdf</t>
   </si>
@@ -234,6 +234,9 @@
 all pages</t>
   </si>
   <si>
+    <t>Header should remain same</t>
+  </si>
+  <si>
     <t>Icons &amp; Text</t>
   </si>
   <si>
@@ -241,6 +244,10 @@
 text</t>
   </si>
   <si>
+    <t>Icons should align with related
+text</t>
+  </si>
+  <si>
     <t>Dropdown Menu</t>
   </si>
   <si>
@@ -248,10 +255,17 @@
 hover/click</t>
   </si>
   <si>
+    <t>Dropdown should open for 
+each menu</t>
+  </si>
+  <si>
     <t>Not found as per as 
 expectation</t>
   </si>
   <si>
+    <t>Failed</t>
+  </si>
+  <si>
     <t>Functional 
 Testing</t>
   </si>
@@ -264,6 +278,9 @@
 clickable</t>
   </si>
   <si>
+    <t>All links should be clickable</t>
+  </si>
+  <si>
     <t>Navigation</t>
   </si>
   <si>
@@ -271,6 +288,9 @@
 clicking header links</t>
   </si>
   <si>
+    <t>Correct page should open</t>
+  </si>
+  <si>
     <t>Logo Navigation</t>
   </si>
   <si>
@@ -278,6 +298,9 @@
 homepage</t>
   </si>
   <si>
+    <t>Homepage should open</t>
+  </si>
+  <si>
     <t>Search Bar</t>
   </si>
   <si>
@@ -285,6 +308,9 @@
 header</t>
   </si>
   <si>
+    <t>Search bar should be visible</t>
+  </si>
+  <si>
     <t>Search Module</t>
   </si>
   <si>
@@ -310,20 +336,35 @@
     <t>Verify search icon presence</t>
   </si>
   <si>
+    <t>Search icon should be visible</t>
+  </si>
+  <si>
     <t>Verify hover effect on icon</t>
+  </si>
+  <si>
+    <t>Hover effect should show</t>
   </si>
   <si>
     <t>Verify search with valid 
 keyword</t>
   </si>
   <si>
+    <t>Correct results should display</t>
+  </si>
+  <si>
     <t>Verify search using Enter key</t>
   </si>
   <si>
+    <t>Search should trigger</t>
+  </si>
+  <si>
     <t>Pagination</t>
   </si>
   <si>
     <t>Verify pagination appears</t>
+  </si>
+  <si>
+    <t>Pagination should display</t>
   </si>
   <si>
     <t>Search Results</t>
@@ -333,7 +374,21 @@
 shown</t>
   </si>
   <si>
+    <t>Related keywords should show</t>
+  </si>
+  <si>
     <t>Footer</t>
+  </si>
+  <si>
+    <t>Footer Section</t>
+  </si>
+  <si>
+    <t>Verify footer section is displayed
+ on the website</t>
+  </si>
+  <si>
+    <t>Footer should be visible in the 
+last on page load</t>
   </si>
   <si>
     <t>Footer Alignment</t>
@@ -343,12 +398,20 @@
 alignment</t>
   </si>
   <si>
+    <t>Footer elements should be 
+properly aligned</t>
+  </si>
+  <si>
     <t>Footer 
 Consistency</t>
   </si>
   <si>
     <t>Verify same footer appears 
 on all pages</t>
+  </si>
+  <si>
+    <t>Verify same footer appears on 
+all pages</t>
   </si>
   <si>
     <t>Follow Us Section</t>
@@ -359,10 +422,17 @@
 section</t>
   </si>
   <si>
+    <t>Verify correctness of social 
+media icons in Follow Us section</t>
+  </si>
+  <si>
     <t>Copyright</t>
   </si>
   <si>
     <t>Verify year &amp; icon displayed</t>
+  </si>
+  <si>
+    <t>Correct year &amp; icon</t>
   </si>
   <si>
     <t>Footer Links</t>
@@ -379,6 +449,10 @@
 correctly</t>
   </si>
   <si>
+    <t>Each icon should open correct 
+social link</t>
+  </si>
+  <si>
     <t>Login Module</t>
   </si>
   <si>
@@ -386,6 +460,9 @@
   </si>
   <si>
     <t>Verify placeholder text in fields</t>
+  </si>
+  <si>
+    <t>Placeholder should guide user</t>
   </si>
   <si>
     <t>Post Login UI</t>
@@ -401,10 +478,17 @@
     <t>Verify spelling mistakes</t>
   </si>
   <si>
+    <t>No spelling errors</t>
+  </si>
+  <si>
     <t>Login Page</t>
   </si>
   <si>
     <t>Verify login page loads properly</t>
+  </si>
+  <si>
+    <t>Login page should load with all
+fields</t>
   </si>
   <si>
     <t>Valid Login</t>
@@ -414,6 +498,9 @@
 number and OTP</t>
   </si>
   <si>
+    <t>User should login successfully</t>
+  </si>
+  <si>
     <t>Invalid Login</t>
   </si>
   <si>
@@ -421,6 +508,9 @@
 phone number</t>
   </si>
   <si>
+    <t>Error message should shown</t>
+  </si>
+  <si>
     <t>Verify error message for invalid
 OTP</t>
   </si>
@@ -431,6 +521,9 @@
     <t>Verify login using Enter key</t>
   </si>
   <si>
+    <t>User should login</t>
+  </si>
+  <si>
     <t>Categories Module (https://www.lerevecraze.com/product-category)</t>
   </si>
   <si>
@@ -444,6 +537,10 @@
 spelled correctly</t>
   </si>
   <si>
+    <t>Verify category names are spelled 
+correctly</t>
+  </si>
+  <si>
     <t>Category Hover</t>
   </si>
   <si>
@@ -451,6 +548,14 @@
 hover for each category</t>
   </si>
   <si>
+    <t>Dropdown menu appears when 
+cursor hovers over category</t>
+  </si>
+  <si>
+    <t>Not working for "Yoga 
+Collection" Category</t>
+  </si>
+  <si>
     <t>Category Click</t>
   </si>
   <si>
@@ -458,11 +563,19 @@
 navigates to category page</t>
   </si>
   <si>
+    <t xml:space="preserve">User is redirected to respective 
+category page
+</t>
+  </si>
+  <si>
     <t>Dropdown Display</t>
   </si>
   <si>
     <t>Verify subcategories are 
 displayed in dropdown</t>
+  </si>
+  <si>
+    <t>All subcategories are visible</t>
   </si>
   <si>
     <t>Product Sorting</t>
@@ -473,12 +586,21 @@
 sorting options</t>
   </si>
   <si>
+    <t>Products should be sorted according 
+to the selected option</t>
+  </si>
+  <si>
     <t>Product Filtering</t>
   </si>
   <si>
     <t>Verify products can be filtered 
 correctly using all available 
 filter options</t>
+  </si>
+  <si>
+    <t>Only products matching the selected 
+filter criteria are displayed. Multiple 
+filters should work together</t>
   </si>
   <si>
     <t>t</t>
@@ -563,7 +685,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -592,6 +714,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF38761D"/>
         <bgColor rgb="FF38761D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor theme="5"/>
       </patternFill>
     </fill>
   </fills>
@@ -656,7 +784,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -742,6 +870,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -1336,8 +1467,8 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="3" max="3" width="14.13"/>
-    <col customWidth="1" min="4" max="4" width="24.0"/>
-    <col customWidth="1" min="5" max="5" width="22.75"/>
+    <col customWidth="1" min="4" max="4" width="25.13"/>
+    <col customWidth="1" min="5" max="5" width="27.88"/>
     <col customWidth="1" min="6" max="6" width="22.88"/>
     <col customWidth="1" min="7" max="7" width="17.63"/>
     <col customWidth="1" min="8" max="8" width="13.88"/>
@@ -1414,103 +1545,111 @@
       <c r="Z5" s="20"/>
     </row>
     <row r="6" ht="31.5" customHeight="1">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="17"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="20"/>
+      <c r="U6" s="20"/>
+      <c r="V6" s="20"/>
+      <c r="W6" s="20"/>
+      <c r="X6" s="20"/>
+      <c r="Y6" s="20"/>
+      <c r="Z6" s="20"/>
+    </row>
+    <row r="7" ht="31.5" customHeight="1">
+      <c r="A7" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="22"/>
-      <c r="O6" s="22"/>
-      <c r="P6" s="22"/>
-      <c r="Q6" s="22"/>
-      <c r="R6" s="22"/>
-      <c r="S6" s="22"/>
-      <c r="T6" s="22"/>
-      <c r="U6" s="22"/>
-      <c r="V6" s="22"/>
-      <c r="W6" s="22"/>
-      <c r="X6" s="22"/>
-      <c r="Y6" s="22"/>
-      <c r="Z6" s="22"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="23">
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22"/>
+      <c r="R7" s="22"/>
+      <c r="S7" s="22"/>
+      <c r="T7" s="22"/>
+      <c r="U7" s="22"/>
+      <c r="V7" s="22"/>
+      <c r="W7" s="22"/>
+      <c r="X7" s="22"/>
+      <c r="Y7" s="22"/>
+      <c r="Z7" s="22"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="23">
         <v>1.0</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B8" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C8" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D8" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E8" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F8" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="26" t="s">
+      <c r="G8" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="H7" s="20"/>
-      <c r="I7" s="27" t="s">
+      <c r="H8" s="20"/>
+      <c r="I8" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="20"/>
-      <c r="N7" s="20"/>
-      <c r="O7" s="20"/>
-      <c r="P7" s="20"/>
-      <c r="Q7" s="20"/>
-      <c r="R7" s="20"/>
-      <c r="S7" s="20"/>
-      <c r="T7" s="20"/>
-      <c r="U7" s="20"/>
-      <c r="V7" s="20"/>
-      <c r="W7" s="20"/>
-      <c r="X7" s="20"/>
-      <c r="Y7" s="20"/>
-      <c r="Z7" s="20"/>
-    </row>
-    <row r="8" ht="48.75" customHeight="1">
-      <c r="A8" s="28">
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="20"/>
+      <c r="S8" s="20"/>
+      <c r="T8" s="20"/>
+      <c r="U8" s="20"/>
+      <c r="V8" s="20"/>
+      <c r="W8" s="20"/>
+      <c r="X8" s="20"/>
+      <c r="Y8" s="20"/>
+      <c r="Z8" s="20"/>
+    </row>
+    <row r="9" ht="48.75" customHeight="1">
+      <c r="A9" s="28">
         <v>2.0</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C9" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="29" t="s">
+      <c r="D9" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E9" s="29" t="s">
         <v>64</v>
-      </c>
-      <c r="F8" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="G8" s="29" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" ht="47.25" customHeight="1">
-      <c r="A9" s="29">
-        <v>3.0</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="E9" s="29" t="s">
-        <v>67</v>
       </c>
       <c r="F9" s="29" t="s">
         <v>59</v>
@@ -1519,143 +1658,191 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" ht="49.5" customHeight="1">
+    <row r="10" ht="47.25" customHeight="1">
       <c r="A10" s="29">
+        <v>3.0</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" s="29" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" ht="49.5" customHeight="1">
+      <c r="A11" s="29">
         <v>4.0</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C11" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="29" t="s">
+      <c r="D11" s="29" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="11" ht="54.0" customHeight="1">
-      <c r="A11" s="29">
+      <c r="E11" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" ht="54.0" customHeight="1">
+      <c r="A12" s="29">
         <v>5.0</v>
       </c>
-      <c r="C11" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="29" t="s">
+      <c r="C12" s="29" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="12" ht="52.5" customHeight="1">
-      <c r="A12" s="29">
+      <c r="D12" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" s="29" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" ht="52.5" customHeight="1">
+      <c r="A13" s="29">
         <v>6.0</v>
       </c>
-      <c r="C12" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="F12" s="29" t="s">
+      <c r="C13" s="29" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="13" ht="46.5" customHeight="1">
-      <c r="B13" s="30" t="s">
+      <c r="D13" s="29" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="14" ht="51.75" customHeight="1">
-      <c r="A14" s="29">
+      <c r="E13" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="I13" s="30" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" ht="46.5" customHeight="1">
+      <c r="B14" s="31" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" ht="51.75" customHeight="1">
+      <c r="A15" s="29">
         <v>7.0</v>
       </c>
-      <c r="C14" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" s="29" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" ht="60.0" customHeight="1">
-      <c r="A15" s="29">
+      <c r="C15" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="E15" s="29" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" ht="60.0" customHeight="1">
+      <c r="A16" s="29">
         <v>8.0</v>
       </c>
-      <c r="C15" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="D15" s="29" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="16" ht="52.5" customHeight="1">
-      <c r="A16" s="29">
-        <v>9.0</v>
-      </c>
       <c r="C16" s="28" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
+      </c>
+      <c r="E16" s="29" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="17" ht="52.5" customHeight="1">
       <c r="A17" s="29">
+        <v>9.0</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="E17" s="29" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" ht="52.5" customHeight="1">
+      <c r="A18" s="29">
         <v>10.0</v>
       </c>
-      <c r="C17" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" s="29" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="18" ht="52.5" customHeight="1">
-      <c r="A18" s="31" t="s">
-        <v>84</v>
+      <c r="C18" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="E18" s="29" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="19" ht="52.5" customHeight="1">
-      <c r="B19" s="29" t="s">
+      <c r="A19" s="32" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" ht="52.5" customHeight="1">
+      <c r="B20" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="29" t="s">
-        <v>85</v>
-      </c>
-      <c r="D19" s="32" t="s">
-        <v>86</v>
-      </c>
-      <c r="E19" s="29" t="s">
-        <v>87</v>
-      </c>
-      <c r="F19" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="G19" s="29" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="20" ht="52.5" customHeight="1">
       <c r="C20" s="29" t="s">
-        <v>90</v>
-      </c>
-      <c r="D20" s="29" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="E20" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="F20" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="G20" s="29" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="21" ht="52.5" customHeight="1">
       <c r="C21" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="D21" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="E21" s="29" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" ht="52.5" customHeight="1">
+      <c r="C22" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="29" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="22" ht="52.5" customHeight="1">
-      <c r="B22" s="29" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="23" ht="62.25" customHeight="1">
-      <c r="C23" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" s="29" t="s">
-        <v>93</v>
+      <c r="D22" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="E22" s="29" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23" ht="52.5" customHeight="1">
+      <c r="B23" s="29" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="24" ht="62.25" customHeight="1">
@@ -1663,240 +1850,337 @@
         <v>31</v>
       </c>
       <c r="D24" s="29" t="s">
-        <v>94</v>
+        <v>103</v>
+      </c>
+      <c r="E24" s="29" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="25" ht="62.25" customHeight="1">
       <c r="C25" s="29" t="s">
-        <v>95</v>
+        <v>31</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>96</v>
+        <v>105</v>
+      </c>
+      <c r="E25" s="29" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="26" ht="62.25" customHeight="1">
       <c r="C26" s="29" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>98</v>
+        <v>108</v>
+      </c>
+      <c r="E26" s="29" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="27" ht="62.25" customHeight="1">
-      <c r="A27" s="31" t="s">
-        <v>99</v>
+      <c r="C27" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="E27" s="29" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="28" ht="62.25" customHeight="1">
-      <c r="B28" s="29" t="s">
+      <c r="A28" s="32" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" ht="62.25" customHeight="1">
+      <c r="B29" s="34" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="29" ht="62.25" customHeight="1">
       <c r="C29" s="29" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>101</v>
+        <v>115</v>
+      </c>
+      <c r="E29" s="29" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="30" ht="62.25" customHeight="1">
       <c r="C30" s="29" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>103</v>
+        <v>118</v>
+      </c>
+      <c r="E30" s="29" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="31" ht="62.25" customHeight="1">
       <c r="C31" s="29" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>105</v>
+        <v>121</v>
+      </c>
+      <c r="E31" s="29" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="32" ht="62.25" customHeight="1">
       <c r="C32" s="29" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>107</v>
+        <v>124</v>
+      </c>
+      <c r="E32" s="29" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="33" ht="62.25" customHeight="1">
-      <c r="B33" s="29" t="s">
-        <v>75</v>
+      <c r="C33" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="D33" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="E33" s="29" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="34" ht="62.25" customHeight="1">
-      <c r="C34" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="D34" s="29" t="s">
-        <v>109</v>
+      <c r="B34" s="29" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="35" ht="62.25" customHeight="1">
       <c r="C35" s="29" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>79</v>
+        <v>130</v>
+      </c>
+      <c r="E35" s="29" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="36" ht="62.25" customHeight="1">
       <c r="C36" s="29" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>111</v>
+        <v>84</v>
+      </c>
+      <c r="E36" s="29" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="37" ht="62.25" customHeight="1">
-      <c r="A37" s="31" t="s">
-        <v>112</v>
+      <c r="C37" s="29" t="s">
+        <v>131</v>
+      </c>
+      <c r="D37" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="E37" s="29" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="38" ht="62.25" customHeight="1">
-      <c r="B38" s="29" t="s">
+      <c r="A38" s="32" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="39" ht="62.25" customHeight="1">
+      <c r="B39" s="32" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="39" ht="62.25" customHeight="1">
-      <c r="C39" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="D39" s="29" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="40" ht="62.25" customHeight="1">
       <c r="C40" s="29" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>116</v>
+        <v>136</v>
+      </c>
+      <c r="E40" s="29" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="41" ht="62.25" customHeight="1">
       <c r="C41" s="29" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>118</v>
+        <v>139</v>
+      </c>
+      <c r="E41" s="29" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="42" ht="62.25" customHeight="1">
-      <c r="B42" s="29" t="s">
-        <v>75</v>
+      <c r="C42" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="D42" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E42" s="29" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="43" ht="62.25" customHeight="1">
-      <c r="C43" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="D43" s="29" t="s">
-        <v>120</v>
+      <c r="B43" s="29" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="44" ht="62.25" customHeight="1">
       <c r="C44" s="29" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>122</v>
+        <v>144</v>
+      </c>
+      <c r="E44" s="29" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="45" ht="62.25" customHeight="1">
       <c r="C45" s="29" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>124</v>
+        <v>147</v>
+      </c>
+      <c r="E45" s="29" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="46" ht="62.25" customHeight="1">
       <c r="C46" s="29" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>125</v>
+        <v>150</v>
+      </c>
+      <c r="E46" s="29" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="47" ht="62.25" customHeight="1">
       <c r="C47" s="29" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>127</v>
+        <v>152</v>
+      </c>
+      <c r="E47" s="29" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="48" ht="62.25" customHeight="1">
-      <c r="A48" s="28" t="s">
-        <v>128</v>
+      <c r="C48" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="D48" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="E48" s="29" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="49" ht="62.25" customHeight="1">
-      <c r="B49" s="29" t="s">
-        <v>129</v>
-      </c>
-      <c r="C49" s="29" t="s">
-        <v>130</v>
-      </c>
-      <c r="D49" s="29" t="s">
-        <v>131</v>
+      <c r="A49" s="28" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="50" ht="62.25" customHeight="1">
-      <c r="B50" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="C50" s="29"/>
-      <c r="D50" s="29"/>
+      <c r="B50" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="C50" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="D50" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="E50" s="29" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="51" ht="62.25" customHeight="1">
-      <c r="B51" s="29"/>
-      <c r="C51" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="D51" s="29" t="s">
-        <v>133</v>
-      </c>
+      <c r="B51" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="C51" s="29"/>
+      <c r="D51" s="29"/>
     </row>
     <row r="52" ht="62.25" customHeight="1">
+      <c r="B52" s="29"/>
       <c r="C52" s="29" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="D52" s="29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="53" ht="61.5" customHeight="1">
+        <v>162</v>
+      </c>
+      <c r="E52" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="F52" s="29" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="53" ht="62.25" customHeight="1">
       <c r="C53" s="29" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
       <c r="D53" s="29" t="s">
-        <v>137</v>
+        <v>166</v>
+      </c>
+      <c r="E53" s="29" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="54" ht="61.5" customHeight="1">
       <c r="C54" s="29" t="s">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="D54" s="29" t="s">
-        <v>139</v>
+        <v>169</v>
+      </c>
+      <c r="E54" s="29" t="s">
+        <v>170</v>
+      </c>
+      <c r="F54" s="29" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="55" ht="61.5" customHeight="1">
       <c r="C55" s="29" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="D55" s="29" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="56" ht="61.5" customHeight="1"/>
+        <v>172</v>
+      </c>
+      <c r="E55" s="29" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="56" ht="61.5" customHeight="1">
+      <c r="C56" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="D56" s="29" t="s">
+        <v>175</v>
+      </c>
+      <c r="E56" s="29" t="s">
+        <v>176</v>
+      </c>
+    </row>
     <row r="57" ht="61.5" customHeight="1"/>
     <row r="58" ht="61.5" customHeight="1"/>
     <row r="59" ht="61.5" customHeight="1"/>
@@ -1906,13 +2190,14 @@
     <row r="63" ht="61.5" customHeight="1"/>
     <row r="64" ht="61.5" customHeight="1"/>
     <row r="65" ht="61.5" customHeight="1"/>
+    <row r="66" ht="61.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A6:I6"/>
-    <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A37:I37"/>
-    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="A49:I49"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="B1"/>
@@ -1930,7 +2215,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="29" t="s">
-        <v>142</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/testCases/Lereve Manual Testing.xlsx
+++ b/testCases/Lereve Manual Testing.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="179">
   <si>
     <t>Please click here to see the full  pdf</t>
   </si>
@@ -261,6 +261,12 @@
   <si>
     <t>Not found as per as 
 expectation</t>
+  </si>
+  <si>
+    <t>1. Open lereve URL .   
+2. Open Homepage
+3. Take mouse pointer 
+on yoga collection</t>
   </si>
   <si>
     <t>Failed</t>
@@ -1694,6 +1700,9 @@
       <c r="F11" s="29" t="s">
         <v>59</v>
       </c>
+      <c r="G11" s="29" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="12" ht="54.0" customHeight="1">
       <c r="A12" s="29">
@@ -1711,6 +1720,9 @@
       <c r="F12" s="29" t="s">
         <v>59</v>
       </c>
+      <c r="G12" s="29" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="13" ht="52.5" customHeight="1">
       <c r="A13" s="29">
@@ -1728,13 +1740,16 @@
       <c r="F13" s="29" t="s">
         <v>77</v>
       </c>
+      <c r="G13" s="29" t="s">
+        <v>78</v>
+      </c>
       <c r="I13" s="30" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" ht="46.5" customHeight="1">
       <c r="B14" s="31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" ht="51.75" customHeight="1">
@@ -1742,13 +1757,16 @@
         <v>7.0</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E15" s="29" t="s">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="F15" s="29" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="16" ht="60.0" customHeight="1">
@@ -1756,13 +1774,16 @@
         <v>8.0</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="F16" s="29" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="17" ht="52.5" customHeight="1">
@@ -1770,13 +1791,16 @@
         <v>9.0</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E17" s="29" t="s">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="F17" s="29" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="18" ht="52.5" customHeight="1">
@@ -1784,18 +1808,21 @@
         <v>10.0</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="F18" s="29" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="19" ht="52.5" customHeight="1">
       <c r="A19" s="32" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" ht="52.5" customHeight="1">
@@ -1803,30 +1830,30 @@
         <v>55</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E20" s="29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G20" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" ht="52.5" customHeight="1">
       <c r="C21" s="29" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E21" s="29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" ht="52.5" customHeight="1">
@@ -1834,15 +1861,15 @@
         <v>31</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E22" s="29" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" ht="52.5" customHeight="1">
       <c r="B23" s="29" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" ht="62.25" customHeight="1">
@@ -1850,10 +1877,10 @@
         <v>31</v>
       </c>
       <c r="D24" s="29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E24" s="29" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" ht="62.25" customHeight="1">
@@ -1861,37 +1888,37 @@
         <v>31</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E25" s="29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" ht="62.25" customHeight="1">
       <c r="C26" s="29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E26" s="29" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" ht="62.25" customHeight="1">
       <c r="C27" s="29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E27" s="29" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" ht="62.25" customHeight="1">
       <c r="A28" s="32" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29" ht="62.25" customHeight="1">
@@ -1899,100 +1926,100 @@
         <v>55</v>
       </c>
       <c r="C29" s="29" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E29" s="29" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" ht="62.25" customHeight="1">
       <c r="C30" s="29" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E30" s="29" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" ht="62.25" customHeight="1">
       <c r="C31" s="29" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E31" s="29" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" ht="62.25" customHeight="1">
       <c r="C32" s="29" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E32" s="29" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" ht="62.25" customHeight="1">
       <c r="C33" s="29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E33" s="29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" ht="62.25" customHeight="1">
       <c r="B34" s="29" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" ht="62.25" customHeight="1">
       <c r="C35" s="29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E35" s="29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36" ht="62.25" customHeight="1">
       <c r="C36" s="29" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E36" s="29" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" ht="62.25" customHeight="1">
       <c r="C37" s="29" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E37" s="29" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" ht="62.25" customHeight="1">
       <c r="A38" s="32" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" ht="62.25" customHeight="1">
@@ -2002,119 +2029,119 @@
     </row>
     <row r="40" ht="62.25" customHeight="1">
       <c r="C40" s="29" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E40" s="29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="41" ht="62.25" customHeight="1">
       <c r="C41" s="29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E41" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="42" ht="62.25" customHeight="1">
       <c r="C42" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E42" s="29" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="43" ht="62.25" customHeight="1">
       <c r="B43" s="29" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" ht="62.25" customHeight="1">
       <c r="C44" s="29" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E44" s="29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="45" ht="62.25" customHeight="1">
       <c r="C45" s="29" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E45" s="29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="46" ht="62.25" customHeight="1">
       <c r="C46" s="29" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E46" s="29" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="47" ht="62.25" customHeight="1">
       <c r="C47" s="29" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D47" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="E47" s="29" t="s">
         <v>152</v>
-      </c>
-      <c r="E47" s="29" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="48" ht="62.25" customHeight="1">
       <c r="C48" s="29" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D48" s="29" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E48" s="29" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="49" ht="62.25" customHeight="1">
       <c r="A49" s="28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="50" ht="62.25" customHeight="1">
       <c r="B50" s="32" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C50" s="29" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D50" s="29" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E50" s="29" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="51" ht="62.25" customHeight="1">
       <c r="B51" s="34" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C51" s="29"/>
       <c r="D51" s="29"/>
@@ -2122,63 +2149,63 @@
     <row r="52" ht="62.25" customHeight="1">
       <c r="B52" s="29"/>
       <c r="C52" s="29" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D52" s="29" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E52" s="29" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F52" s="29" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="53" ht="62.25" customHeight="1">
       <c r="C53" s="29" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D53" s="29" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E53" s="29" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="54" ht="61.5" customHeight="1">
       <c r="C54" s="29" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D54" s="29" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E54" s="29" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F54" s="29" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="55" ht="61.5" customHeight="1">
       <c r="C55" s="29" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D55" s="29" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E55" s="29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="56" ht="61.5" customHeight="1">
       <c r="C56" s="29" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D56" s="29" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E56" s="29" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="57" ht="61.5" customHeight="1"/>
@@ -2215,7 +2242,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="29" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/testCases/Lereve Manual Testing.xlsx
+++ b/testCases/Lereve Manual Testing.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="185">
   <si>
     <t>Please click here to see the full  pdf</t>
   </si>
@@ -358,19 +358,31 @@
     <t>Correct results should display</t>
   </si>
   <si>
+    <t>Search returns empty results 
+even with valid keywords</t>
+  </si>
+  <si>
+    <t>1. open Lereve URL
+2. Go to search bar
+3. Search any valid 
+keyword. like:  "tunic"</t>
+  </si>
+  <si>
+    <t>click</t>
+  </si>
+  <si>
     <t>Verify search using Enter key</t>
   </si>
   <si>
     <t>Search should trigger</t>
   </si>
   <si>
-    <t>Pagination</t>
-  </si>
-  <si>
-    <t>Verify pagination appears</t>
-  </si>
-  <si>
-    <t>Pagination should display</t>
+    <t>1. open Lereve URL
+2. Go to search bar
+3. Search any valid 
+keyword. like:  "tunic"
+4. press enter from key
+board</t>
   </si>
   <si>
     <t>Search Results</t>
@@ -383,6 +395,21 @@
     <t>Related keywords should show</t>
   </si>
   <si>
+    <t>No related keywords or 
+suggestions displayed. Search 
+returns no results.</t>
+  </si>
+  <si>
+    <t>1. Click Search icon
+2. Type "Shirt"
+3. Observe dropdown</t>
+  </si>
+  <si>
+    <t>BLOCKED
+ (blocked by the 
+main search bug)</t>
+  </si>
+  <si>
     <t>Footer</t>
   </si>
   <si>
@@ -416,20 +443,19 @@
 on all pages</t>
   </si>
   <si>
-    <t>Verify same footer appears on 
-all pages</t>
-  </si>
-  <si>
-    <t>Follow Us Section</t>
+    <t>Footer should remain same</t>
+  </si>
+  <si>
+    <t>Social Media Icons</t>
   </si>
   <si>
     <t>Verify correctness of social 
-media icons in Follow Us 
-section</t>
-  </si>
-  <si>
-    <t>Verify correctness of social 
-media icons in Follow Us section</t>
+media icons in Footer section</t>
+  </si>
+  <si>
+    <t>Each social media platform icon 
+should appear only once and with 
+correct icons</t>
   </si>
   <si>
     <t>Copyright</t>
@@ -543,8 +569,8 @@
 spelled correctly</t>
   </si>
   <si>
-    <t>Verify category names are spelled 
-correctly</t>
+    <t>All category names should be 
+spelled correctly</t>
   </si>
   <si>
     <t>Category Hover</t>
@@ -556,10 +582,6 @@
   <si>
     <t>Dropdown menu appears when 
 cursor hovers over category</t>
-  </si>
-  <si>
-    <t>Not working for "Yoga 
-Collection" Category</t>
   </si>
   <si>
     <t>Category Click</t>
@@ -607,6 +629,19 @@
     <t>Only products matching the selected 
 filter criteria are displayed. Multiple 
 filters should work together</t>
+  </si>
+  <si>
+    <t>Infinite Scroll</t>
+  </si>
+  <si>
+    <t>Verify products load automatically
+ on scroll (infinite scroll)</t>
+  </si>
+  <si>
+    <t>New products should load automatically 
+as user scrolls down. Loading indicator 
+should appear. Scroll stops at footer 
+when all products are loaded.</t>
   </si>
   <si>
     <t>t</t>
@@ -1472,12 +1507,13 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="14.13"/>
-    <col customWidth="1" min="4" max="4" width="25.13"/>
-    <col customWidth="1" min="5" max="5" width="27.88"/>
-    <col customWidth="1" min="6" max="6" width="22.88"/>
+    <col customWidth="1" min="3" max="3" width="15.38"/>
+    <col customWidth="1" min="4" max="4" width="25.63"/>
+    <col customWidth="1" min="5" max="5" width="30.25"/>
+    <col customWidth="1" min="6" max="6" width="23.38"/>
     <col customWidth="1" min="7" max="7" width="17.63"/>
     <col customWidth="1" min="8" max="8" width="13.88"/>
+    <col customWidth="1" min="9" max="9" width="13.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1768,6 +1804,9 @@
       <c r="F15" s="29" t="s">
         <v>59</v>
       </c>
+      <c r="G15" s="29" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="16" ht="60.0" customHeight="1">
       <c r="A16" s="29">
@@ -1785,6 +1824,9 @@
       <c r="F16" s="29" t="s">
         <v>59</v>
       </c>
+      <c r="G16" s="29" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="17" ht="52.5" customHeight="1">
       <c r="A17" s="29">
@@ -1802,6 +1844,9 @@
       <c r="F17" s="29" t="s">
         <v>59</v>
       </c>
+      <c r="G17" s="29" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="18" ht="52.5" customHeight="1">
       <c r="A18" s="29">
@@ -1819,6 +1864,9 @@
       <c r="F18" s="29" t="s">
         <v>59</v>
       </c>
+      <c r="G18" s="29" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="19" ht="52.5" customHeight="1">
       <c r="A19" s="32" t="s">
@@ -1855,6 +1903,12 @@
       <c r="E21" s="29" t="s">
         <v>101</v>
       </c>
+      <c r="F21" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="G21" s="29" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="22" ht="52.5" customHeight="1">
       <c r="C22" s="29" t="s">
@@ -1882,330 +1936,414 @@
       <c r="E24" s="29" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="25" ht="62.25" customHeight="1">
+      <c r="F24" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="G24" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I24" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" ht="78.0" customHeight="1">
       <c r="C25" s="29" t="s">
         <v>31</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E25" s="29" t="s">
-        <v>107</v>
+        <v>110</v>
+      </c>
+      <c r="F25" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="G25" s="29" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="26" ht="62.25" customHeight="1">
       <c r="C26" s="29" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E26" s="29" t="s">
-        <v>110</v>
+        <v>114</v>
+      </c>
+      <c r="F26" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="G26" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="I26" s="29" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="27" ht="62.25" customHeight="1">
-      <c r="C27" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="D27" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="E27" s="29" t="s">
-        <v>113</v>
+      <c r="A27" s="32" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="28" ht="62.25" customHeight="1">
-      <c r="A28" s="32" t="s">
-        <v>114</v>
+      <c r="B28" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="D28" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="E28" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="F28" s="29" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="29" ht="62.25" customHeight="1">
-      <c r="B29" s="34" t="s">
-        <v>55</v>
-      </c>
       <c r="C29" s="29" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E29" s="29" t="s">
-        <v>117</v>
+        <v>124</v>
+      </c>
+      <c r="F29" s="29" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="30" ht="62.25" customHeight="1">
       <c r="C30" s="29" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="E30" s="29" t="s">
-        <v>120</v>
+        <v>127</v>
+      </c>
+      <c r="F30" s="29" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="31" ht="62.25" customHeight="1">
       <c r="C31" s="29" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E31" s="29" t="s">
-        <v>123</v>
+        <v>130</v>
+      </c>
+      <c r="F31" s="29" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="32" ht="62.25" customHeight="1">
       <c r="C32" s="29" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="E32" s="29" t="s">
-        <v>126</v>
+        <v>133</v>
+      </c>
+      <c r="F32" s="29" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="33" ht="62.25" customHeight="1">
-      <c r="C33" s="29" t="s">
-        <v>127</v>
-      </c>
-      <c r="D33" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="E33" s="29" t="s">
-        <v>129</v>
+      <c r="B33" s="29" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="34" ht="62.25" customHeight="1">
-      <c r="B34" s="29" t="s">
-        <v>80</v>
+      <c r="C34" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="D34" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="E34" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="F34" s="29" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="35" ht="62.25" customHeight="1">
       <c r="C35" s="29" t="s">
-        <v>130</v>
+        <v>84</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="E35" s="29" t="s">
-        <v>83</v>
+        <v>86</v>
+      </c>
+      <c r="F35" s="29" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="36" ht="62.25" customHeight="1">
       <c r="C36" s="29" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="E36" s="29" t="s">
-        <v>86</v>
+        <v>138</v>
+      </c>
+      <c r="F36" s="29" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="37" ht="62.25" customHeight="1">
-      <c r="C37" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="D37" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="E37" s="29" t="s">
-        <v>134</v>
+      <c r="A37" s="32" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="38" ht="62.25" customHeight="1">
-      <c r="A38" s="32" t="s">
-        <v>135</v>
+      <c r="B38" s="32" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="39" ht="62.25" customHeight="1">
-      <c r="B39" s="32" t="s">
-        <v>55</v>
+      <c r="C39" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="D39" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E39" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="F39" s="29" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="40" ht="62.25" customHeight="1">
       <c r="C40" s="29" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E40" s="29" t="s">
-        <v>138</v>
+        <v>144</v>
+      </c>
+      <c r="F40" s="29" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="41" ht="62.25" customHeight="1">
       <c r="C41" s="29" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E41" s="29" t="s">
-        <v>140</v>
+        <v>147</v>
+      </c>
+      <c r="F41" s="29" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="42" ht="62.25" customHeight="1">
-      <c r="C42" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="D42" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="E42" s="29" t="s">
-        <v>143</v>
+      <c r="B42" s="29" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="43" ht="62.25" customHeight="1">
-      <c r="B43" s="29" t="s">
-        <v>80</v>
+      <c r="C43" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="D43" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="E43" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="F43" s="29" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="44" ht="62.25" customHeight="1">
       <c r="C44" s="29" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="E44" s="29" t="s">
-        <v>146</v>
+        <v>153</v>
+      </c>
+      <c r="F44" s="29" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="45" ht="62.25" customHeight="1">
       <c r="C45" s="29" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="E45" s="29" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" ht="62.25" customHeight="1">
       <c r="C46" s="29" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E46" s="29" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="47" ht="62.25" customHeight="1">
       <c r="C47" s="29" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E47" s="29" t="s">
-        <v>152</v>
+        <v>160</v>
+      </c>
+      <c r="F47" s="29" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="48" ht="62.25" customHeight="1">
-      <c r="C48" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="D48" s="29" t="s">
-        <v>155</v>
-      </c>
-      <c r="E48" s="29" t="s">
-        <v>156</v>
+      <c r="A48" s="32" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="49" ht="62.25" customHeight="1">
-      <c r="A49" s="28" t="s">
-        <v>157</v>
+      <c r="B49" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="C49" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="D49" s="29" t="s">
+        <v>164</v>
+      </c>
+      <c r="E49" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="F49" s="29" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="50" ht="62.25" customHeight="1">
-      <c r="B50" s="32" t="s">
-        <v>158</v>
-      </c>
-      <c r="C50" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="D50" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="E50" s="29" t="s">
-        <v>161</v>
-      </c>
+      <c r="B50" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="C50" s="29"/>
+      <c r="D50" s="29"/>
     </row>
     <row r="51" ht="62.25" customHeight="1">
-      <c r="B51" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="C51" s="29"/>
-      <c r="D51" s="29"/>
+      <c r="B51" s="29"/>
+      <c r="C51" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="D51" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="E51" s="29" t="s">
+        <v>168</v>
+      </c>
+      <c r="F51" s="29" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="52" ht="62.25" customHeight="1">
-      <c r="B52" s="29"/>
       <c r="C52" s="29" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="D52" s="29" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="E52" s="29" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="F52" s="29" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="53" ht="62.25" customHeight="1">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="53" ht="61.5" customHeight="1">
       <c r="C53" s="29" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D53" s="29" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E53" s="29" t="s">
-        <v>168</v>
+        <v>174</v>
+      </c>
+      <c r="F53" s="29" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="54" ht="61.5" customHeight="1">
       <c r="C54" s="29" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D54" s="29" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E54" s="29" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F54" s="29" t="s">
-        <v>165</v>
+        <v>97</v>
       </c>
     </row>
     <row r="55" ht="61.5" customHeight="1">
       <c r="C55" s="29" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D55" s="29" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E55" s="29" t="s">
-        <v>174</v>
+        <v>180</v>
+      </c>
+      <c r="F55" s="29" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="56" ht="61.5" customHeight="1">
       <c r="C56" s="29" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D56" s="29" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E56" s="29" t="s">
-        <v>177</v>
+        <v>183</v>
+      </c>
+      <c r="F56" s="29" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="57" ht="61.5" customHeight="1"/>
@@ -2217,19 +2355,19 @@
     <row r="63" ht="61.5" customHeight="1"/>
     <row r="64" ht="61.5" customHeight="1"/>
     <row r="65" ht="61.5" customHeight="1"/>
-    <row r="66" ht="61.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A38:I38"/>
-    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A48:I48"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="B1"/>
+    <hyperlink r:id="rId2" ref="H24"/>
   </hyperlinks>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -2242,7 +2380,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="29" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>

--- a/testCases/Lereve Manual Testing.xlsx
+++ b/testCases/Lereve Manual Testing.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="197">
   <si>
     <t>Please click here to see the full  pdf</t>
   </si>
@@ -424,6 +424,10 @@
 last on page load</t>
   </si>
   <si>
+    <t>1.Open  Lereve URL                                        
+2. Go to footer</t>
+  </si>
+  <si>
     <t>Footer Alignment</t>
   </si>
   <si>
@@ -497,6 +501,9 @@
     <t>Placeholder should guide user</t>
   </si>
   <si>
+    <t>1. Open login page</t>
+  </si>
+  <si>
     <t>Post Login UI</t>
   </si>
   <si>
@@ -504,6 +511,11 @@
 login</t>
   </si>
   <si>
+    <t>1. Open login page
+2. Do login with valid 
+OTP and Phone number</t>
+  </si>
+  <si>
     <t>Spelling</t>
   </si>
   <si>
@@ -533,6 +545,10 @@
     <t>User should login successfully</t>
   </si>
   <si>
+    <t>1. Enter valid credentials
+2. Click Login</t>
+  </si>
+  <si>
     <t>Invalid Login</t>
   </si>
   <si>
@@ -556,6 +572,11 @@
     <t>User should login</t>
   </si>
   <si>
+    <t>1. Open login page
+2.Enter valid credentials
+3. Press Enter Key</t>
+  </si>
+  <si>
     <t>Categories Module (https://www.lerevecraze.com/product-category)</t>
   </si>
   <si>
@@ -573,6 +594,13 @@
 spelled correctly</t>
   </si>
   <si>
+    <t>1. Open Le Reve website
+2. View main navigation 
+menu
+3. Check spelling of all
+ categories</t>
+  </si>
+  <si>
     <t>Category Hover</t>
   </si>
   <si>
@@ -582,6 +610,13 @@
   <si>
     <t>Dropdown menu appears when 
 cursor hovers over category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open homepage
+2. Hover over each 
+category
+3. Observe dropdown
+</t>
   </si>
   <si>
     <t>Category Click</t>
@@ -596,6 +631,12 @@
 </t>
   </si>
   <si>
+    <t>1. Open homepage
+2. Click each category
+3. Verify page redirects 
+correctly</t>
+  </si>
+  <si>
     <t>Dropdown Display</t>
   </si>
   <si>
@@ -604,6 +645,13 @@
   </si>
   <si>
     <t>All subcategories are visible</t>
+  </si>
+  <si>
+    <t>1. Open homepage
+2. Hover over all the 
+categories
+3. Check subcategories 
+visibility</t>
   </si>
   <si>
     <t>Product Sorting</t>
@@ -618,6 +666,12 @@
 to the selected option</t>
   </si>
   <si>
+    <t>1. Open category page
+2. Test each sorting option
+3. Verify correct order for 
+each</t>
+  </si>
+  <si>
     <t>Product Filtering</t>
   </si>
   <si>
@@ -629,6 +683,13 @@
     <t>Only products matching the selected 
 filter criteria are displayed. Multiple 
 filters should work together</t>
+  </si>
+  <si>
+    <t>1. Open category page
+2. Apply each filter
+3. Verify products update
+4. Test multiple filters 
+together</t>
   </si>
   <si>
     <t>Infinite Scroll</t>
@@ -642,6 +703,13 @@
 as user scrolls down. Loading indicator 
 should appear. Scroll stops at footer 
 when all products are loaded.</t>
+  </si>
+  <si>
+    <t>1. Open any category page 
+2. Scroll down the page 
+continuously
+3. Observe if new products 
+load automatically</t>
   </si>
   <si>
     <t>t</t>
@@ -1511,7 +1579,7 @@
     <col customWidth="1" min="4" max="4" width="25.63"/>
     <col customWidth="1" min="5" max="5" width="30.25"/>
     <col customWidth="1" min="6" max="6" width="23.38"/>
-    <col customWidth="1" min="7" max="7" width="17.63"/>
+    <col customWidth="1" min="7" max="7" width="20.38"/>
     <col customWidth="1" min="8" max="8" width="13.88"/>
     <col customWidth="1" min="9" max="9" width="13.5"/>
   </cols>
@@ -2007,61 +2075,76 @@
       <c r="F28" s="29" t="s">
         <v>97</v>
       </c>
+      <c r="G28" s="29" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="29" ht="62.25" customHeight="1">
       <c r="C29" s="29" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E29" s="29" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F29" s="29" t="s">
         <v>97</v>
       </c>
+      <c r="G29" s="29" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="30" ht="62.25" customHeight="1">
       <c r="C30" s="29" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E30" s="29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F30" s="29" t="s">
         <v>97</v>
       </c>
+      <c r="G30" s="29" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="31" ht="62.25" customHeight="1">
       <c r="C31" s="29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E31" s="29" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F31" s="29" t="s">
         <v>97</v>
       </c>
+      <c r="G31" s="29" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="32" ht="62.25" customHeight="1">
       <c r="C32" s="29" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E32" s="29" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F32" s="29" t="s">
         <v>97</v>
+      </c>
+      <c r="G32" s="29" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="33" ht="62.25" customHeight="1">
@@ -2071,16 +2154,19 @@
     </row>
     <row r="34" ht="62.25" customHeight="1">
       <c r="C34" s="29" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E34" s="29" t="s">
         <v>83</v>
       </c>
       <c r="F34" s="29" t="s">
         <v>97</v>
+      </c>
+      <c r="G34" s="29" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="35" ht="62.25" customHeight="1">
@@ -2096,24 +2182,30 @@
       <c r="F35" s="29" t="s">
         <v>97</v>
       </c>
+      <c r="G35" s="29" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="36" ht="62.25" customHeight="1">
       <c r="C36" s="29" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E36" s="29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F36" s="29" t="s">
         <v>97</v>
       </c>
+      <c r="G36" s="29" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="37" ht="62.25" customHeight="1">
       <c r="A37" s="32" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="38" ht="62.25" customHeight="1">
@@ -2123,44 +2215,53 @@
     </row>
     <row r="39" ht="62.25" customHeight="1">
       <c r="C39" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E39" s="29" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F39" s="29" t="s">
         <v>97</v>
       </c>
+      <c r="G39" s="29" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="40" ht="62.25" customHeight="1">
       <c r="C40" s="29" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E40" s="29" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F40" s="29" t="s">
         <v>97</v>
       </c>
+      <c r="G40" s="29" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="41" ht="62.25" customHeight="1">
       <c r="C41" s="29" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E41" s="29" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F41" s="29" t="s">
         <v>97</v>
+      </c>
+      <c r="G41" s="29" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="42" ht="62.25" customHeight="1">
@@ -2170,88 +2271,106 @@
     </row>
     <row r="43" ht="62.25" customHeight="1">
       <c r="C43" s="29" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E43" s="29" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F43" s="29" t="s">
         <v>97</v>
       </c>
+      <c r="G43" s="29" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="44" ht="62.25" customHeight="1">
       <c r="C44" s="29" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E44" s="29" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F44" s="29" t="s">
         <v>97</v>
       </c>
+      <c r="G44" s="29" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="45" ht="62.25" customHeight="1">
       <c r="C45" s="29" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E45" s="29" t="s">
-        <v>156</v>
+        <v>160</v>
+      </c>
+      <c r="G45" s="29" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="46" ht="62.25" customHeight="1">
       <c r="C46" s="29" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D46" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="E46" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="G46" s="29" t="s">
         <v>157</v>
-      </c>
-      <c r="E46" s="29" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="47" ht="62.25" customHeight="1">
       <c r="C47" s="29" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E47" s="29" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F47" s="29" t="s">
         <v>97</v>
       </c>
+      <c r="G47" s="29" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="48" ht="62.25" customHeight="1">
       <c r="A48" s="32" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="49" ht="62.25" customHeight="1">
       <c r="B49" s="32" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C49" s="29" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D49" s="29" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E49" s="29" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="F49" s="29" t="s">
         <v>97</v>
+      </c>
+      <c r="G49" s="29" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="50" ht="62.25" customHeight="1">
@@ -2264,86 +2383,104 @@
     <row r="51" ht="62.25" customHeight="1">
       <c r="B51" s="29"/>
       <c r="C51" s="29" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D51" s="29" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E51" s="29" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="F51" s="29" t="s">
         <v>97</v>
       </c>
+      <c r="G51" s="29" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="52" ht="62.25" customHeight="1">
       <c r="C52" s="29" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D52" s="29" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="E52" s="29" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="F52" s="29" t="s">
         <v>97</v>
       </c>
+      <c r="G52" s="29" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="53" ht="61.5" customHeight="1">
       <c r="C53" s="29" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D53" s="29" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E53" s="29" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="F53" s="29" t="s">
         <v>97</v>
       </c>
+      <c r="G53" s="29" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="54" ht="61.5" customHeight="1">
       <c r="C54" s="29" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="D54" s="29" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="E54" s="29" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="F54" s="29" t="s">
         <v>97</v>
       </c>
+      <c r="G54" s="29" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="55" ht="61.5" customHeight="1">
       <c r="C55" s="29" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="D55" s="29" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="E55" s="29" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="F55" s="29" t="s">
         <v>97</v>
       </c>
+      <c r="G55" s="29" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="56" ht="61.5" customHeight="1">
       <c r="C56" s="29" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="D56" s="29" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="E56" s="29" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="F56" s="29" t="s">
         <v>97</v>
+      </c>
+      <c r="G56" s="29" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="57" ht="61.5" customHeight="1"/>
@@ -2380,7 +2517,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="29" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/testCases/Lereve Manual Testing.xlsx
+++ b/testCases/Lereve Manual Testing.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="199">
   <si>
     <t>Please click here to see the full  pdf</t>
   </si>
@@ -269,6 +269,9 @@
 on yoga collection</t>
   </si>
   <si>
+    <t>click here</t>
+  </si>
+  <si>
     <t>Failed</t>
   </si>
   <si>
@@ -345,10 +348,10 @@
     <t>Search icon should be visible</t>
   </si>
   <si>
-    <t>Verify hover effect on icon</t>
-  </si>
-  <si>
-    <t>Hover effect should show</t>
+    <t>Verify placeholder text is present</t>
+  </si>
+  <si>
+    <t>Placeholder text should be visible</t>
   </si>
   <si>
     <t>Verify search with valid 
@@ -366,9 +369,6 @@
 2. Go to search bar
 3. Search any valid 
 keyword. like:  "tunic"</t>
-  </si>
-  <si>
-    <t>click</t>
   </si>
   <si>
     <t>Verify search using Enter key</t>
@@ -559,8 +559,17 @@
     <t>Error message should shown</t>
   </si>
   <si>
+    <t>1. Enter invalid Phone 
+Number
+2. Click Login</t>
+  </si>
+  <si>
     <t>Verify error message for invalid
 OTP</t>
+  </si>
+  <si>
+    <t>1. Enter invalid OTP
+2. Click Login</t>
   </si>
   <si>
     <t>Keyboard</t>
@@ -722,7 +731,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -782,19 +791,29 @@
     </font>
     <font>
       <b/>
+      <sz val="12.0"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <color rgb="FF0000FF"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12.0"/>
+      <color rgb="FF0000FF"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -821,14 +840,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF38761D"/>
-        <bgColor rgb="FF38761D"/>
+        <fgColor theme="7"/>
+        <bgColor theme="7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor theme="6"/>
       </patternFill>
     </fill>
   </fills>
@@ -893,7 +918,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="40">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -965,8 +990,8 @@
     <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
@@ -978,7 +1003,13 @@
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+      <alignment readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -986,13 +1017,22 @@
     <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="top"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -1579,7 +1619,7 @@
     <col customWidth="1" min="4" max="4" width="25.63"/>
     <col customWidth="1" min="5" max="5" width="30.25"/>
     <col customWidth="1" min="6" max="6" width="23.38"/>
-    <col customWidth="1" min="7" max="7" width="20.38"/>
+    <col customWidth="1" min="7" max="7" width="21.0"/>
     <col customWidth="1" min="8" max="8" width="13.88"/>
     <col customWidth="1" min="9" max="9" width="13.5"/>
   </cols>
@@ -1711,10 +1751,10 @@
       <c r="B8" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="26" t="s">
         <v>57</v>
       </c>
       <c r="E8" s="26" t="s">
@@ -1767,9 +1807,12 @@
       <c r="G9" s="29" t="s">
         <v>60</v>
       </c>
+      <c r="I9" s="30" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="10" ht="47.25" customHeight="1">
-      <c r="A10" s="29">
+      <c r="A10" s="28">
         <v>3.0</v>
       </c>
       <c r="C10" s="29" t="s">
@@ -1787,9 +1830,12 @@
       <c r="G10" s="29" t="s">
         <v>60</v>
       </c>
+      <c r="I10" s="30" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="11" ht="49.5" customHeight="1">
-      <c r="A11" s="29">
+      <c r="A11" s="28">
         <v>4.0</v>
       </c>
       <c r="C11" s="29" t="s">
@@ -1807,9 +1853,12 @@
       <c r="G11" s="29" t="s">
         <v>60</v>
       </c>
+      <c r="I11" s="30" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="12" ht="54.0" customHeight="1">
-      <c r="A12" s="29">
+      <c r="A12" s="28">
         <v>5.0</v>
       </c>
       <c r="C12" s="29" t="s">
@@ -1827,9 +1876,12 @@
       <c r="G12" s="29" t="s">
         <v>60</v>
       </c>
+      <c r="I12" s="30" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="13" ht="52.5" customHeight="1">
-      <c r="A13" s="29">
+      <c r="A13" s="28">
         <v>6.0</v>
       </c>
       <c r="C13" s="29" t="s">
@@ -1847,27 +1899,30 @@
       <c r="G13" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="I13" s="30" t="s">
+      <c r="H13" s="31" t="s">
         <v>79</v>
       </c>
+      <c r="I13" s="32" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="14" ht="46.5" customHeight="1">
-      <c r="B14" s="31" t="s">
-        <v>80</v>
+      <c r="B14" s="33" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="15" ht="51.75" customHeight="1">
-      <c r="A15" s="29">
+      <c r="A15" s="28">
         <v>7.0</v>
       </c>
-      <c r="C15" s="28" t="s">
-        <v>81</v>
+      <c r="C15" s="34" t="s">
+        <v>82</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E15" s="29" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F15" s="29" t="s">
         <v>59</v>
@@ -1875,19 +1930,22 @@
       <c r="G15" s="29" t="s">
         <v>60</v>
       </c>
+      <c r="I15" s="30" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="16" ht="60.0" customHeight="1">
-      <c r="A16" s="29">
+      <c r="A16" s="28">
         <v>8.0</v>
       </c>
-      <c r="C16" s="28" t="s">
-        <v>84</v>
+      <c r="C16" s="34" t="s">
+        <v>85</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F16" s="29" t="s">
         <v>59</v>
@@ -1895,19 +1953,22 @@
       <c r="G16" s="29" t="s">
         <v>60</v>
       </c>
+      <c r="I16" s="30" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="17" ht="52.5" customHeight="1">
-      <c r="A17" s="29">
+      <c r="A17" s="28">
         <v>9.0</v>
       </c>
-      <c r="C17" s="28" t="s">
-        <v>87</v>
+      <c r="C17" s="34" t="s">
+        <v>88</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E17" s="29" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F17" s="29" t="s">
         <v>59</v>
@@ -1915,19 +1976,22 @@
       <c r="G17" s="29" t="s">
         <v>60</v>
       </c>
+      <c r="I17" s="30" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="18" ht="52.5" customHeight="1">
-      <c r="A18" s="29">
+      <c r="A18" s="28">
         <v>10.0</v>
       </c>
-      <c r="C18" s="31" t="s">
-        <v>90</v>
+      <c r="C18" s="35" t="s">
+        <v>91</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F18" s="29" t="s">
         <v>59</v>
@@ -1935,89 +1999,122 @@
       <c r="G18" s="29" t="s">
         <v>60</v>
       </c>
+      <c r="I18" s="30" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="19" ht="52.5" customHeight="1">
-      <c r="A19" s="32" t="s">
-        <v>93</v>
+      <c r="A19" s="33" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="20" ht="52.5" customHeight="1">
-      <c r="B20" s="29" t="s">
+      <c r="A20" s="28">
+        <v>11.0</v>
+      </c>
+      <c r="B20" s="36" t="s">
         <v>55</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="D20" s="33" t="s">
         <v>95</v>
       </c>
+      <c r="D20" s="29" t="s">
+        <v>96</v>
+      </c>
       <c r="E20" s="29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G20" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="I20" s="30" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" ht="52.5" customHeight="1">
+      <c r="A21" s="28">
+        <v>12.0</v>
+      </c>
+      <c r="C21" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="E21" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="F21" s="29" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="21" ht="52.5" customHeight="1">
-      <c r="C21" s="29" t="s">
+      <c r="G21" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="D21" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="E21" s="29" t="s">
-        <v>101</v>
-      </c>
-      <c r="F21" s="29" t="s">
-        <v>97</v>
-      </c>
-      <c r="G21" s="29" t="s">
-        <v>98</v>
+      <c r="I21" s="30" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="22" ht="52.5" customHeight="1">
+      <c r="A22" s="28">
+        <v>13.0</v>
+      </c>
       <c r="C22" s="29" t="s">
         <v>31</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E22" s="29" t="s">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="F22" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="G22" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="I22" s="30" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="23" ht="52.5" customHeight="1">
-      <c r="B23" s="29" t="s">
-        <v>80</v>
+      <c r="B23" s="36" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="24" ht="62.25" customHeight="1">
+      <c r="A24" s="28">
+        <v>14.0</v>
+      </c>
       <c r="C24" s="29" t="s">
         <v>31</v>
       </c>
       <c r="D24" s="29" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E24" s="29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F24" s="29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G24" s="29" t="s">
-        <v>107</v>
-      </c>
-      <c r="H24" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I24" s="30" t="s">
+      <c r="H24" s="37" t="s">
         <v>79</v>
       </c>
+      <c r="I24" s="32" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="25" ht="78.0" customHeight="1">
+      <c r="A25" s="28">
+        <v>15.0</v>
+      </c>
       <c r="C25" s="29" t="s">
         <v>31</v>
       </c>
@@ -2028,13 +2125,19 @@
         <v>110</v>
       </c>
       <c r="F25" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G25" s="29" t="s">
         <v>111</v>
       </c>
+      <c r="I25" s="30" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="26" ht="62.25" customHeight="1">
+      <c r="A26" s="28">
+        <v>16.0</v>
+      </c>
       <c r="C26" s="29" t="s">
         <v>112</v>
       </c>
@@ -2050,17 +2153,20 @@
       <c r="G26" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="I26" s="29" t="s">
+      <c r="I26" s="38" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="27" ht="62.25" customHeight="1">
-      <c r="A27" s="32" t="s">
+      <c r="A27" s="33" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="28" ht="62.25" customHeight="1">
-      <c r="B28" s="34" t="s">
+      <c r="A28" s="28">
+        <v>17.0</v>
+      </c>
+      <c r="B28" s="36" t="s">
         <v>55</v>
       </c>
       <c r="C28" s="29" t="s">
@@ -2073,13 +2179,19 @@
         <v>121</v>
       </c>
       <c r="F28" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G28" s="29" t="s">
         <v>122</v>
       </c>
+      <c r="I28" s="30" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="29" ht="62.25" customHeight="1">
+      <c r="A29" s="28">
+        <v>18.0</v>
+      </c>
       <c r="C29" s="29" t="s">
         <v>123</v>
       </c>
@@ -2090,13 +2202,19 @@
         <v>125</v>
       </c>
       <c r="F29" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G29" s="29" t="s">
         <v>122</v>
       </c>
+      <c r="I29" s="30" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="30" ht="62.25" customHeight="1">
+      <c r="A30" s="28">
+        <v>19.0</v>
+      </c>
       <c r="C30" s="29" t="s">
         <v>126</v>
       </c>
@@ -2107,13 +2225,19 @@
         <v>128</v>
       </c>
       <c r="F30" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G30" s="29" t="s">
         <v>122</v>
       </c>
+      <c r="I30" s="30" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="31" ht="62.25" customHeight="1">
+      <c r="A31" s="28">
+        <v>20.0</v>
+      </c>
       <c r="C31" s="29" t="s">
         <v>129</v>
       </c>
@@ -2124,13 +2248,19 @@
         <v>131</v>
       </c>
       <c r="F31" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G31" s="29" t="s">
         <v>122</v>
       </c>
+      <c r="I31" s="30" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="32" ht="62.25" customHeight="1">
+      <c r="A32" s="28">
+        <v>21.0</v>
+      </c>
       <c r="C32" s="29" t="s">
         <v>132</v>
       </c>
@@ -2141,18 +2271,24 @@
         <v>134</v>
       </c>
       <c r="F32" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G32" s="29" t="s">
         <v>122</v>
       </c>
+      <c r="I32" s="30" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="33" ht="62.25" customHeight="1">
-      <c r="B33" s="29" t="s">
-        <v>80</v>
+      <c r="B33" s="36" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="34" ht="62.25" customHeight="1">
+      <c r="A34" s="28">
+        <v>22.0</v>
+      </c>
       <c r="C34" s="29" t="s">
         <v>135</v>
       </c>
@@ -2160,33 +2296,45 @@
         <v>136</v>
       </c>
       <c r="E34" s="29" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F34" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G34" s="29" t="s">
         <v>122</v>
       </c>
+      <c r="I34" s="30" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="35" ht="62.25" customHeight="1">
+      <c r="A35" s="28">
+        <v>23.0</v>
+      </c>
       <c r="C35" s="29" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E35" s="29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F35" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G35" s="29" t="s">
         <v>122</v>
       </c>
+      <c r="I35" s="30" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="36" ht="62.25" customHeight="1">
+      <c r="A36" s="28">
+        <v>24.0</v>
+      </c>
       <c r="C36" s="29" t="s">
         <v>137</v>
       </c>
@@ -2197,23 +2345,29 @@
         <v>139</v>
       </c>
       <c r="F36" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G36" s="29" t="s">
         <v>122</v>
       </c>
+      <c r="I36" s="30" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="37" ht="62.25" customHeight="1">
-      <c r="A37" s="32" t="s">
+      <c r="A37" s="33" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="38" ht="62.25" customHeight="1">
-      <c r="B38" s="32" t="s">
+      <c r="B38" s="33" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="39" ht="62.25" customHeight="1">
+      <c r="A39" s="28">
+        <v>25.0</v>
+      </c>
       <c r="C39" s="29" t="s">
         <v>141</v>
       </c>
@@ -2224,13 +2378,19 @@
         <v>143</v>
       </c>
       <c r="F39" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G39" s="29" t="s">
         <v>144</v>
       </c>
+      <c r="I39" s="30" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="40" ht="62.25" customHeight="1">
+      <c r="A40" s="28">
+        <v>26.0</v>
+      </c>
       <c r="C40" s="29" t="s">
         <v>145</v>
       </c>
@@ -2241,13 +2401,19 @@
         <v>146</v>
       </c>
       <c r="F40" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G40" s="29" t="s">
         <v>147</v>
       </c>
+      <c r="I40" s="30" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="41" ht="62.25" customHeight="1">
+      <c r="A41" s="28">
+        <v>27.0</v>
+      </c>
       <c r="C41" s="29" t="s">
         <v>148</v>
       </c>
@@ -2258,18 +2424,24 @@
         <v>150</v>
       </c>
       <c r="F41" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G41" s="29" t="s">
         <v>144</v>
       </c>
+      <c r="I41" s="30" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="42" ht="62.25" customHeight="1">
-      <c r="B42" s="29" t="s">
-        <v>80</v>
+      <c r="B42" s="36" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="43" ht="62.25" customHeight="1">
+      <c r="A43" s="28">
+        <v>28.0</v>
+      </c>
       <c r="C43" s="29" t="s">
         <v>151</v>
       </c>
@@ -2280,13 +2452,19 @@
         <v>153</v>
       </c>
       <c r="F43" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G43" s="29" t="s">
         <v>144</v>
       </c>
+      <c r="I43" s="30" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="44" ht="62.25" customHeight="1">
+      <c r="A44" s="28">
+        <v>29.0</v>
+      </c>
       <c r="C44" s="29" t="s">
         <v>154</v>
       </c>
@@ -2297,13 +2475,19 @@
         <v>156</v>
       </c>
       <c r="F44" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G44" s="29" t="s">
         <v>157</v>
       </c>
+      <c r="I44" s="30" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="45" ht="62.25" customHeight="1">
+      <c r="A45" s="28">
+        <v>30.0</v>
+      </c>
       <c r="C45" s="29" t="s">
         <v>158</v>
       </c>
@@ -2313,174 +2497,237 @@
       <c r="E45" s="29" t="s">
         <v>160</v>
       </c>
+      <c r="F45" s="29" t="s">
+        <v>98</v>
+      </c>
       <c r="G45" s="29" t="s">
-        <v>157</v>
+        <v>161</v>
+      </c>
+      <c r="I45" s="30" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="46" ht="62.25" customHeight="1">
+      <c r="A46" s="28">
+        <v>31.0</v>
+      </c>
       <c r="C46" s="29" t="s">
         <v>158</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E46" s="29" t="s">
         <v>160</v>
       </c>
+      <c r="F46" s="29" t="s">
+        <v>98</v>
+      </c>
       <c r="G46" s="29" t="s">
-        <v>157</v>
+        <v>163</v>
+      </c>
+      <c r="I46" s="30" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="47" ht="62.25" customHeight="1">
+      <c r="A47" s="28">
+        <v>32.0</v>
+      </c>
       <c r="C47" s="29" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E47" s="29" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F47" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G47" s="29" t="s">
-        <v>165</v>
+        <v>167</v>
+      </c>
+      <c r="I47" s="30" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="48" ht="62.25" customHeight="1">
-      <c r="A48" s="32" t="s">
-        <v>166</v>
+      <c r="A48" s="33" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="49" ht="62.25" customHeight="1">
-      <c r="B49" s="32" t="s">
-        <v>167</v>
+      <c r="A49" s="28">
+        <v>33.0</v>
+      </c>
+      <c r="B49" s="33" t="s">
+        <v>169</v>
       </c>
       <c r="C49" s="29" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D49" s="29" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E49" s="29" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F49" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G49" s="29" t="s">
-        <v>171</v>
+        <v>173</v>
+      </c>
+      <c r="I49" s="30" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="50" ht="62.25" customHeight="1">
-      <c r="B50" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="C50" s="29"/>
-      <c r="D50" s="29"/>
+      <c r="B50" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C50" s="39"/>
+      <c r="D50" s="39"/>
     </row>
     <row r="51" ht="62.25" customHeight="1">
-      <c r="B51" s="29"/>
+      <c r="A51" s="28">
+        <v>34.0</v>
+      </c>
+      <c r="B51" s="39"/>
       <c r="C51" s="29" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D51" s="29" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E51" s="29" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F51" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G51" s="29" t="s">
-        <v>175</v>
+        <v>177</v>
+      </c>
+      <c r="I51" s="30" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="52" ht="62.25" customHeight="1">
+      <c r="A52" s="28">
+        <v>35.0</v>
+      </c>
       <c r="C52" s="29" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D52" s="29" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E52" s="29" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F52" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G52" s="29" t="s">
-        <v>179</v>
+        <v>181</v>
+      </c>
+      <c r="I52" s="30" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="53" ht="61.5" customHeight="1">
+      <c r="A53" s="28">
+        <v>36.0</v>
+      </c>
       <c r="C53" s="29" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D53" s="29" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E53" s="29" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F53" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G53" s="29" t="s">
-        <v>183</v>
+        <v>185</v>
+      </c>
+      <c r="I53" s="30" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="54" ht="61.5" customHeight="1">
+      <c r="A54" s="28">
+        <v>37.0</v>
+      </c>
       <c r="C54" s="29" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D54" s="29" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E54" s="29" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F54" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G54" s="29" t="s">
-        <v>187</v>
+        <v>189</v>
+      </c>
+      <c r="I54" s="30" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="55" ht="61.5" customHeight="1">
+      <c r="A55" s="28">
+        <v>38.0</v>
+      </c>
       <c r="C55" s="29" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D55" s="29" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E55" s="29" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F55" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G55" s="29" t="s">
-        <v>191</v>
+        <v>193</v>
+      </c>
+      <c r="I55" s="30" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="56" ht="61.5" customHeight="1">
+      <c r="A56" s="28">
+        <v>39.0</v>
+      </c>
       <c r="C56" s="29" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D56" s="29" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E56" s="29" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F56" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G56" s="29" t="s">
-        <v>195</v>
+        <v>197</v>
+      </c>
+      <c r="I56" s="30" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="57" ht="61.5" customHeight="1"/>
@@ -2502,9 +2749,10 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="B1"/>
-    <hyperlink r:id="rId2" ref="H24"/>
+    <hyperlink r:id="rId2" ref="H13"/>
+    <hyperlink r:id="rId3" ref="H24"/>
   </hyperlinks>
-  <drawing r:id="rId3"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -2516,8 +2764,8 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="s">
-        <v>196</v>
+      <c r="A1" s="39" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>
